--- a/data/trans_bre/IP16B01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Clase-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 12,19</t>
+          <t>-35,44; 12,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 49,73</t>
+          <t>6,54; 47,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 15,04</t>
+          <t>-38,4; 14,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 98,9</t>
+          <t>6,99; 92,0</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,12</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,54; -7,55</t>
+          <t>-40,35; -7,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 2,31</t>
+          <t>-53,46; 2,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,54; -7,55</t>
+          <t>-40,35; -7,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 2,39</t>
+          <t>-57,15; 2,83</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,52</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 33,2</t>
+          <t>-43,21; 36,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,92</t>
+          <t>0,0; 44,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 49,78</t>
+          <t>-45,8; 63,42</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,74; -7,49</t>
+          <t>-35,42; -6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 23,51</t>
+          <t>-14,1; 25,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -8,37</t>
+          <t>-36,51; -6,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 36,97</t>
+          <t>-15,34; 38,46</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 11,45</t>
+          <t>-25,04; 8,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 7,61</t>
+          <t>-34,41; 8,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 12,97</t>
+          <t>-26,97; 9,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 8,53</t>
+          <t>-37,54; 7,83</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 15,92</t>
+          <t>-47,98; 15,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,88; -7,83</t>
+          <t>-64,47; -8,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 18,84</t>
+          <t>-52,21; 18,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,88; -7,83</t>
+          <t>-64,47; -8,08</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,59; -3,65</t>
+          <t>-19,13; -3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 3,26</t>
+          <t>-17,36; 3,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -4,18</t>
+          <t>-20,06; -3,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 3,98</t>
+          <t>-18,92; 3,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B01-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B01-Clase-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 12,42</t>
+          <t>-33,82; 12,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 47,97</t>
+          <t>6,58; 50,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 14,49</t>
+          <t>-37,02; 15,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 92,0</t>
+          <t>7,04; 102,18</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 21,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -7,64</t>
+          <t>-39,35; -7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 2,54</t>
+          <t>-52,53; 1,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -7,64</t>
+          <t>-39,35; -7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,15; 2,83</t>
+          <t>-53,98; 2,12</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,62</t>
+          <t>0,0; 30,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 36,74</t>
+          <t>-43,41; 32,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,13</t>
+          <t>0,0; 44,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,8; 63,42</t>
+          <t>-46,16; 52,35</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,42; -6,38</t>
+          <t>-36,37; -7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 25,9</t>
+          <t>-14,46; 23,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,51; -6,81</t>
+          <t>-37,49; -8,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 38,46</t>
+          <t>-16,17; 35,61</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 8,74</t>
+          <t>-25,47; 8,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 8,19</t>
+          <t>-37,79; 5,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 9,81</t>
+          <t>-27,14; 9,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 7,83</t>
+          <t>-39,88; 6,2</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 15,91</t>
+          <t>-48,63; 15,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,47; -8,08</t>
+          <t>-64,46; -8,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 18,87</t>
+          <t>-54,67; 18,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,47; -8,08</t>
+          <t>-64,46; -8,57</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,13; -3,21</t>
+          <t>-19,32; -4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 3,08</t>
+          <t>-17,14; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -3,6</t>
+          <t>-20,26; -4,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 3,66</t>
+          <t>-18,78; 4,68</t>
         </is>
       </c>
     </row>
